--- a/Na-aba/home/data/가스공사 의뢰서.xlsx
+++ b/Na-aba/home/data/가스공사 의뢰서.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\-\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjch2\Desktop\보고서\Project PROVIDENCE\Request\PMI\Na-aba\home\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01402F7B-E947-4FC6-81E3-909DECA5FBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12990"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월5일-1" sheetId="1" r:id="rId1"/>
@@ -17,17 +18,16 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="_" hidden="1">#REF!</definedName>
     <definedName name="___" hidden="1">#REF!</definedName>
-    <definedName name="_Fill" hidden="1">'[2]토목-물가'!#REF!</definedName>
+    <definedName name="_Fill" hidden="1">'[1]토목-물가'!#REF!</definedName>
     <definedName name="_Key1" hidden="1">#REF!</definedName>
     <definedName name="_Key2" hidden="1">#REF!</definedName>
     <definedName name="_Order1" hidden="1">0</definedName>
     <definedName name="_Order2" hidden="1">0</definedName>
-    <definedName name="_Parse_Out" hidden="1">'[3]갑지(추정)'!#REF!</definedName>
+    <definedName name="_Parse_Out" hidden="1">'[2]갑지(추정)'!#REF!</definedName>
     <definedName name="_Regression_Int" hidden="1">1</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
     <definedName name="_Table1_In2" hidden="1">#REF!</definedName>
@@ -97,17 +97,26 @@
     <definedName name="ㅎㅎㅎㅎㅎ" hidden="1">{#N/A,#N/A,FALSE,"표지"}</definedName>
     <definedName name="ㅗㅗㅗ" hidden="1">{#N/A,#N/A,FALSE,"부대1"}</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="78">
   <si>
     <t>용접 및 비파괴 검사 기록서</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -336,10 +345,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>P1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HS2025-04-095</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -385,10 +390,6 @@
   </si>
   <si>
     <t>○</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>P1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -455,7 +456,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="&quot;4303 - &quot;000"/>
     <numFmt numFmtId="177" formatCode="000"/>
@@ -971,30 +972,501 @@
   </cellStyleXfs>
   <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1002,6 +1474,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1011,26 +1486,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1049,467 +1509,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1548,7 +1549,7 @@
         <xdr:cNvPr id="2" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8ED25D83-E28C-4687-93D8-FFC802CC0AAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ED25D83-E28C-4687-93D8-FFC802CC0AAE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1632,7 +1633,7 @@
         <xdr:cNvPr id="3" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C07F62BF-FA66-484F-9168-8386BB0CEAD6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C07F62BF-FA66-484F-9168-8386BB0CEAD6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1702,46 +1703,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="6월5일-1"/>
-      <sheetName val="6월6일-2"/>
-      <sheetName val="6월7일-3"/>
-      <sheetName val="6월11일-4"/>
-      <sheetName val="6월13일-5"/>
-      <sheetName val="6월16일-6"/>
-      <sheetName val="6월18일-7"/>
-      <sheetName val="6월19일-8"/>
-      <sheetName val="6월25일-9"/>
-      <sheetName val="6월25일-9R"/>
-      <sheetName val="6월26일-10"/>
-      <sheetName val="6월27일-11"/>
-      <sheetName val="6월30일-11R"/>
-      <sheetName val="6월30일-12"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="정보-총원가(TO)"/>
@@ -1765,8 +1727,8 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="GAEYO"/>
@@ -2596,1265 +2558,1398 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP32"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" customWidth="1"/>
-    <col min="5" max="6" width="6.77734375" customWidth="1"/>
-    <col min="7" max="7" width="3.44140625" customWidth="1"/>
-    <col min="8" max="8" width="5.77734375" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="11" width="5.77734375" customWidth="1"/>
-    <col min="12" max="12" width="6.77734375" customWidth="1"/>
-    <col min="13" max="15" width="2.21875" customWidth="1"/>
-    <col min="16" max="16" width="4.44140625" customWidth="1"/>
-    <col min="17" max="25" width="2.88671875" customWidth="1"/>
-    <col min="26" max="26" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.59765625" customWidth="1"/>
+    <col min="3" max="3" width="12.296875" customWidth="1"/>
+    <col min="4" max="4" width="8.59765625" customWidth="1"/>
+    <col min="5" max="6" width="6.796875" customWidth="1"/>
+    <col min="7" max="7" width="3.3984375" customWidth="1"/>
+    <col min="8" max="8" width="5.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="11" width="5.796875" customWidth="1"/>
+    <col min="12" max="12" width="6.796875" customWidth="1"/>
+    <col min="13" max="15" width="2.19921875" customWidth="1"/>
+    <col min="16" max="16" width="4.3984375" customWidth="1"/>
+    <col min="17" max="25" width="2.8984375" customWidth="1"/>
+    <col min="26" max="26" width="3.296875" customWidth="1"/>
     <col min="27" max="28" width="3" customWidth="1"/>
-    <col min="32" max="32" width="10.109375" customWidth="1"/>
+    <col min="32" max="32" width="10.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:41" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="4" t="s">
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
+      <c r="M1" s="164"/>
+      <c r="N1" s="164"/>
+      <c r="O1" s="164"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="6">
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="169">
         <v>1</v>
       </c>
-      <c r="U1" s="6"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="7"/>
+      <c r="U1" s="169"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="3"/>
     </row>
-    <row r="2" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="12" t="s">
+    <row r="2" spans="1:41" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
+      <c r="I2" s="167"/>
+      <c r="J2" s="167"/>
+      <c r="K2" s="167"/>
+      <c r="L2" s="167"/>
+      <c r="M2" s="167"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="15">
+      <c r="R2" s="171"/>
+      <c r="S2" s="171"/>
+      <c r="T2" s="171"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="172">
         <v>1</v>
       </c>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="16"/>
+      <c r="W2" s="172"/>
+      <c r="X2" s="172"/>
+      <c r="Y2" s="172"/>
+      <c r="Z2" s="172"/>
+      <c r="AA2" s="172"/>
+      <c r="AB2" s="173"/>
     </row>
-    <row r="3" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:41" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="21" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="174" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="23"/>
+      <c r="R3" s="175"/>
+      <c r="S3" s="175"/>
+      <c r="T3" s="175"/>
+      <c r="U3" s="175"/>
+      <c r="V3" s="175"/>
+      <c r="W3" s="175"/>
+      <c r="X3" s="175"/>
+      <c r="Y3" s="175"/>
+      <c r="Z3" s="175"/>
+      <c r="AA3" s="175"/>
+      <c r="AB3" s="176"/>
     </row>
-    <row r="4" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:41" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="27" t="s">
+      <c r="B4" s="178"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
+      <c r="L4" s="178"/>
+      <c r="M4" s="178"/>
+      <c r="N4" s="178"/>
+      <c r="O4" s="178"/>
+      <c r="P4" s="179"/>
+      <c r="Q4" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="29"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="180"/>
     </row>
-    <row r="5" spans="1:41" s="8" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:41" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32" t="s">
+      <c r="B5" s="147"/>
+      <c r="C5" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="34" t="s">
+      <c r="D5" s="154"/>
+      <c r="E5" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="31"/>
-      <c r="G5" s="34" t="s">
+      <c r="F5" s="147"/>
+      <c r="G5" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36">
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="157">
         <v>45813</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="34" t="s">
+      <c r="M5" s="158"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
+      <c r="P5" s="159"/>
+      <c r="Q5" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="39">
+      <c r="R5" s="146"/>
+      <c r="S5" s="146"/>
+      <c r="T5" s="146"/>
+      <c r="U5" s="146"/>
+      <c r="V5" s="146"/>
+      <c r="W5" s="146"/>
+      <c r="X5" s="147"/>
+      <c r="Y5" s="123">
         <v>45813</v>
       </c>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="40"/>
-      <c r="AB5" s="41"/>
+      <c r="Z5" s="124"/>
+      <c r="AA5" s="124"/>
+      <c r="AB5" s="125"/>
     </row>
-    <row r="6" spans="1:41" s="8" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="42"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="53"/>
-      <c r="Z6" s="54"/>
-      <c r="AA6" s="54"/>
-      <c r="AB6" s="55"/>
+    <row r="6" spans="1:41" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="152"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="155"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="160"/>
+      <c r="M6" s="161"/>
+      <c r="N6" s="161"/>
+      <c r="O6" s="161"/>
+      <c r="P6" s="162"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="115"/>
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115"/>
+      <c r="X6" s="116"/>
+      <c r="Y6" s="126"/>
+      <c r="Z6" s="127"/>
+      <c r="AA6" s="127"/>
+      <c r="AB6" s="128"/>
     </row>
-    <row r="7" spans="1:41" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="56" t="s">
+    <row r="7" spans="1:41" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="129" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="58" t="s">
+      <c r="B7" s="130"/>
+      <c r="C7" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="59"/>
-      <c r="E7" s="46" t="s">
+      <c r="D7" s="134"/>
+      <c r="E7" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="47"/>
-      <c r="G7" s="60" t="s">
+      <c r="F7" s="138"/>
+      <c r="G7" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="34" t="s">
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="27" t="s">
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="65" t="s">
+      <c r="R7" s="118"/>
+      <c r="S7" s="118"/>
+      <c r="T7" s="118"/>
+      <c r="U7" s="118"/>
+      <c r="V7" s="118"/>
+      <c r="W7" s="119"/>
+      <c r="X7" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="Y7" s="65" t="s">
+      <c r="Y7" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="Z7" s="66" t="s">
+      <c r="Z7" s="148" t="s">
         <v>20</v>
       </c>
-      <c r="AA7" s="67" t="s">
+      <c r="AA7" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="AB7" s="68" t="s">
+      <c r="AB7" s="111" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:41" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="69"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="76" t="s">
+    <row r="8" spans="1:41" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="131"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="144"/>
+      <c r="L8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="48" t="s">
+      <c r="M8" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="27" t="s">
+      <c r="N8" s="115"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="64"/>
-      <c r="X8" s="77"/>
-      <c r="Y8" s="77"/>
-      <c r="Z8" s="78"/>
-      <c r="AA8" s="79"/>
-      <c r="AB8" s="80"/>
+      <c r="R8" s="118"/>
+      <c r="S8" s="118"/>
+      <c r="T8" s="118"/>
+      <c r="U8" s="118"/>
+      <c r="V8" s="118"/>
+      <c r="W8" s="119"/>
+      <c r="X8" s="103"/>
+      <c r="Y8" s="103"/>
+      <c r="Z8" s="149"/>
+      <c r="AA8" s="109"/>
+      <c r="AB8" s="112"/>
     </row>
-    <row r="9" spans="1:41" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="81" t="s">
+    <row r="9" spans="1:41" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="82" t="s">
+      <c r="D9" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="82" t="s">
+      <c r="F9" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="82" t="s">
+      <c r="G9" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="82" t="s">
+      <c r="H9" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="82" t="s">
+      <c r="I9" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="82" t="s">
+      <c r="J9" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="82" t="s">
+      <c r="K9" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="83" t="s">
+      <c r="L9" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="M9" s="65" t="s">
+      <c r="M9" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="N9" s="65" t="s">
+      <c r="N9" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="65" t="s">
+      <c r="O9" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="P9" s="82" t="s">
+      <c r="P9" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="Q9" s="65">
+      <c r="Q9" s="102">
         <v>1</v>
       </c>
-      <c r="R9" s="65">
+      <c r="R9" s="102">
         <v>2</v>
       </c>
-      <c r="S9" s="65">
+      <c r="S9" s="102">
         <v>3</v>
       </c>
-      <c r="T9" s="65">
+      <c r="T9" s="102">
         <v>4</v>
       </c>
-      <c r="U9" s="65">
+      <c r="U9" s="102">
         <v>5</v>
       </c>
-      <c r="V9" s="65">
+      <c r="V9" s="102">
         <v>6</v>
       </c>
-      <c r="W9" s="65">
+      <c r="W9" s="102">
         <v>7</v>
       </c>
-      <c r="X9" s="77"/>
-      <c r="Y9" s="77"/>
-      <c r="Z9" s="78"/>
-      <c r="AA9" s="79"/>
-      <c r="AB9" s="80"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="103"/>
+      <c r="Z9" s="149"/>
+      <c r="AA9" s="109"/>
+      <c r="AB9" s="112"/>
     </row>
-    <row r="10" spans="1:41" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="84"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="77"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="77"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="77"/>
-      <c r="R10" s="77"/>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
-      <c r="U10" s="77"/>
-      <c r="V10" s="77"/>
-      <c r="W10" s="77"/>
-      <c r="X10" s="77"/>
-      <c r="Y10" s="77"/>
-      <c r="Z10" s="78"/>
-      <c r="AA10" s="79"/>
-      <c r="AB10" s="80"/>
+    <row r="10" spans="1:41" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="121"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="103"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="103"/>
+      <c r="O10" s="103"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="103"/>
+      <c r="R10" s="103"/>
+      <c r="S10" s="103"/>
+      <c r="T10" s="103"/>
+      <c r="U10" s="103"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103"/>
+      <c r="Y10" s="103"/>
+      <c r="Z10" s="149"/>
+      <c r="AA10" s="109"/>
+      <c r="AB10" s="112"/>
     </row>
-    <row r="11" spans="1:41" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="84"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="77"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="77"/>
-      <c r="S11" s="77"/>
-      <c r="T11" s="77"/>
-      <c r="U11" s="77"/>
-      <c r="V11" s="77"/>
-      <c r="W11" s="77"/>
-      <c r="X11" s="77"/>
-      <c r="Y11" s="77"/>
-      <c r="Z11" s="78"/>
-      <c r="AA11" s="79"/>
-      <c r="AB11" s="80"/>
+    <row r="11" spans="1:41" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="121"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="103"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="106"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="103"/>
+      <c r="U11" s="103"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="103"/>
+      <c r="Y11" s="103"/>
+      <c r="Z11" s="149"/>
+      <c r="AA11" s="109"/>
+      <c r="AB11" s="112"/>
     </row>
-    <row r="12" spans="1:41" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="84"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
-      <c r="U12" s="77"/>
-      <c r="V12" s="77"/>
-      <c r="W12" s="77"/>
-      <c r="X12" s="77"/>
-      <c r="Y12" s="77"/>
-      <c r="Z12" s="78"/>
-      <c r="AA12" s="79"/>
-      <c r="AB12" s="80"/>
+    <row r="12" spans="1:41" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="121"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="103"/>
+      <c r="V12" s="103"/>
+      <c r="W12" s="103"/>
+      <c r="X12" s="103"/>
+      <c r="Y12" s="103"/>
+      <c r="Z12" s="149"/>
+      <c r="AA12" s="109"/>
+      <c r="AB12" s="112"/>
     </row>
-    <row r="13" spans="1:41" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="85"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="87"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="86"/>
-      <c r="N13" s="86"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="86"/>
-      <c r="R13" s="86"/>
-      <c r="S13" s="86"/>
-      <c r="T13" s="86"/>
-      <c r="U13" s="86"/>
-      <c r="V13" s="86"/>
-      <c r="W13" s="86"/>
-      <c r="X13" s="86"/>
-      <c r="Y13" s="86"/>
-      <c r="Z13" s="88"/>
-      <c r="AA13" s="89"/>
-      <c r="AB13" s="90"/>
+    <row r="13" spans="1:41" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="122"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="104"/>
+      <c r="S13" s="104"/>
+      <c r="T13" s="104"/>
+      <c r="U13" s="104"/>
+      <c r="V13" s="104"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="104"/>
+      <c r="Y13" s="104"/>
+      <c r="Z13" s="150"/>
+      <c r="AA13" s="110"/>
+      <c r="AB13" s="113"/>
     </row>
-    <row r="14" spans="1:41" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="91">
+    <row r="14" spans="1:41" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="90">
         <v>1</v>
       </c>
-      <c r="B14" s="92">
+      <c r="B14" s="100">
         <v>63</v>
       </c>
-      <c r="C14" s="93" t="s">
+      <c r="C14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="94" t="s">
+      <c r="D14" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="95" t="s">
+      <c r="E14" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="96" t="s">
+      <c r="F14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="97" t="s">
+      <c r="G14" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="98" t="s">
+      <c r="H14" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="98" t="s">
+      <c r="I14" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="97" t="s">
+      <c r="J14" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="97" t="s">
+      <c r="K14" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="99"/>
-      <c r="M14" s="97" t="s">
+      <c r="L14" s="86"/>
+      <c r="M14" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="N14" s="97"/>
-      <c r="O14" s="97"/>
-      <c r="P14" s="100" t="s">
+      <c r="N14" s="62"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="Q14" s="97" t="s">
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="62"/>
+      <c r="W14" s="62"/>
+      <c r="X14" s="62"/>
+      <c r="Y14" s="62"/>
+      <c r="Z14" s="62"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="64"/>
+    </row>
+    <row r="15" spans="1:41" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="91"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="R14" s="97">
-        <v>1</v>
-      </c>
-      <c r="S14" s="97">
-        <v>1</v>
-      </c>
-      <c r="T14" s="97">
-        <v>1</v>
-      </c>
-      <c r="U14" s="97">
-        <v>1</v>
-      </c>
-      <c r="V14" s="97">
-        <v>1</v>
-      </c>
-      <c r="W14" s="97">
-        <v>1</v>
-      </c>
-      <c r="X14" s="97"/>
-      <c r="Y14" s="97"/>
-      <c r="Z14" s="97"/>
-      <c r="AA14" s="101"/>
-      <c r="AB14" s="102"/>
+      <c r="D15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="63"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="63"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="63"/>
+      <c r="S15" s="63"/>
+      <c r="T15" s="63"/>
+      <c r="U15" s="63"/>
+      <c r="V15" s="63"/>
+      <c r="W15" s="63"/>
+      <c r="X15" s="63"/>
+      <c r="Y15" s="63"/>
+      <c r="Z15" s="63"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="65"/>
+      <c r="AF15" s="18"/>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="20"/>
+      <c r="AK15" s="20"/>
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="20"/>
+      <c r="AN15" s="20"/>
+      <c r="AO15" s="21"/>
     </row>
-    <row r="15" spans="1:41" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="103"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="93" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="105" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="95" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="106" t="s">
+    <row r="16" spans="1:41" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="90">
+        <v>2</v>
+      </c>
+      <c r="B16" s="100">
+        <v>64</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="107"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="107"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="109"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="107"/>
-      <c r="O15" s="107"/>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="107"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="107"/>
-      <c r="T15" s="107"/>
-      <c r="U15" s="107"/>
-      <c r="V15" s="107"/>
-      <c r="W15" s="107"/>
-      <c r="X15" s="107"/>
-      <c r="Y15" s="107"/>
-      <c r="Z15" s="107"/>
-      <c r="AA15" s="111"/>
-      <c r="AB15" s="112"/>
-      <c r="AF15" s="113"/>
-      <c r="AH15" s="114"/>
-      <c r="AI15" s="115"/>
-      <c r="AK15" s="115"/>
-      <c r="AL15" s="114"/>
-      <c r="AM15" s="115"/>
-      <c r="AN15" s="115"/>
-      <c r="AO15" s="116"/>
+      <c r="D16" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="97" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" s="86"/>
+      <c r="M16" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="62"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="88" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q16" s="62"/>
+      <c r="R16" s="62"/>
+      <c r="S16" s="62"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="62"/>
+      <c r="W16" s="62"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="62"/>
+      <c r="Z16" s="62"/>
+      <c r="AA16" s="30"/>
+      <c r="AB16" s="64"/>
     </row>
-    <row r="16" spans="1:41" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="91">
-        <v>2</v>
-      </c>
-      <c r="B16" s="92">
+    <row r="17" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="91"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="93" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="94" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="96" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="98" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="98" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="97" t="s">
-        <v>61</v>
-      </c>
-      <c r="K16" s="97" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="99"/>
-      <c r="M16" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="N16" s="97"/>
-      <c r="O16" s="97"/>
-      <c r="P16" s="100" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q16" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="R16" s="97">
-        <v>1</v>
-      </c>
-      <c r="S16" s="97">
-        <v>1</v>
-      </c>
-      <c r="T16" s="97" t="s">
-        <v>51</v>
-      </c>
-      <c r="U16" s="97">
-        <v>1</v>
-      </c>
-      <c r="V16" s="97">
-        <v>1</v>
-      </c>
-      <c r="W16" s="97">
-        <v>1</v>
-      </c>
-      <c r="X16" s="97"/>
-      <c r="Y16" s="97"/>
-      <c r="Z16" s="97"/>
-      <c r="AA16" s="101"/>
-      <c r="AB16" s="102"/>
+      <c r="E17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="63"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="63"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="63"/>
+      <c r="R17" s="63"/>
+      <c r="S17" s="63"/>
+      <c r="T17" s="63"/>
+      <c r="U17" s="63"/>
+      <c r="V17" s="63"/>
+      <c r="W17" s="63"/>
+      <c r="X17" s="63"/>
+      <c r="Y17" s="63"/>
+      <c r="Z17" s="63"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="65"/>
+      <c r="AF17" s="18"/>
+      <c r="AG17" s="99"/>
+      <c r="AH17" s="19"/>
+      <c r="AI17" s="20"/>
+      <c r="AJ17" s="94"/>
+      <c r="AK17" s="20"/>
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="20"/>
+      <c r="AN17" s="20"/>
+      <c r="AO17" s="21"/>
+      <c r="AP17" s="94"/>
     </row>
-    <row r="17" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="103"/>
-      <c r="B17" s="104"/>
-      <c r="C17" s="117" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="105" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="95" t="s">
+    <row r="18" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="90"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="88"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="62"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="62"/>
+      <c r="V18" s="62"/>
+      <c r="W18" s="62"/>
+      <c r="X18" s="62"/>
+      <c r="Y18" s="62"/>
+      <c r="Z18" s="62"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="64"/>
+      <c r="AF18" s="18"/>
+      <c r="AG18" s="99"/>
+      <c r="AH18" s="19"/>
+      <c r="AI18" s="20"/>
+      <c r="AJ18" s="94"/>
+      <c r="AK18" s="20"/>
+      <c r="AL18" s="20"/>
+      <c r="AM18" s="20"/>
+      <c r="AN18" s="20"/>
+      <c r="AO18" s="21"/>
+      <c r="AP18" s="94"/>
+    </row>
+    <row r="19" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="91"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="63"/>
+      <c r="P19" s="89"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="63"/>
+      <c r="S19" s="63"/>
+      <c r="T19" s="63"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="63"/>
+      <c r="W19" s="63"/>
+      <c r="X19" s="63"/>
+      <c r="Y19" s="63"/>
+      <c r="Z19" s="63"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="65"/>
+    </row>
+    <row r="20" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="90"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="88"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="62"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="62"/>
+      <c r="W20" s="62"/>
+      <c r="X20" s="62"/>
+      <c r="Y20" s="62"/>
+      <c r="Z20" s="62"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="64"/>
+    </row>
+    <row r="21" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="91"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="89"/>
+      <c r="Q21" s="63"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="63"/>
+      <c r="T21" s="63"/>
+      <c r="U21" s="63"/>
+      <c r="V21" s="63"/>
+      <c r="W21" s="63"/>
+      <c r="X21" s="63"/>
+      <c r="Y21" s="63"/>
+      <c r="Z21" s="63"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="65"/>
+    </row>
+    <row r="22" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="90"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="62"/>
+      <c r="X22" s="62"/>
+      <c r="Y22" s="62"/>
+      <c r="Z22" s="62"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="64"/>
+    </row>
+    <row r="23" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="91"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+      <c r="K23" s="63"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="63"/>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="63"/>
+      <c r="R23" s="63"/>
+      <c r="S23" s="63"/>
+      <c r="T23" s="63"/>
+      <c r="U23" s="63"/>
+      <c r="V23" s="63"/>
+      <c r="W23" s="63"/>
+      <c r="X23" s="63"/>
+      <c r="Y23" s="63"/>
+      <c r="Z23" s="63"/>
+      <c r="AA23" s="33"/>
+      <c r="AB23" s="65"/>
+    </row>
+    <row r="24" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="90"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="88"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="62"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="62"/>
+      <c r="Z24" s="62"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="64"/>
+    </row>
+    <row r="25" spans="1:42" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="91"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="87"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="63"/>
+      <c r="P25" s="89"/>
+      <c r="Q25" s="63"/>
+      <c r="R25" s="63"/>
+      <c r="S25" s="63"/>
+      <c r="T25" s="63"/>
+      <c r="U25" s="63"/>
+      <c r="V25" s="63"/>
+      <c r="W25" s="63"/>
+      <c r="X25" s="63"/>
+      <c r="Y25" s="63"/>
+      <c r="Z25" s="63"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="65"/>
+    </row>
+    <row r="26" spans="1:42" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="B26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="107"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="107"/>
-      <c r="N17" s="107"/>
-      <c r="O17" s="107"/>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="107"/>
-      <c r="R17" s="107"/>
-      <c r="S17" s="107"/>
-      <c r="T17" s="107"/>
-      <c r="U17" s="107"/>
-      <c r="V17" s="107"/>
-      <c r="W17" s="107"/>
-      <c r="X17" s="107"/>
-      <c r="Y17" s="107"/>
-      <c r="Z17" s="107"/>
-      <c r="AA17" s="111"/>
-      <c r="AB17" s="112"/>
-      <c r="AF17" s="113"/>
-      <c r="AG17" s="118"/>
-      <c r="AH17" s="114"/>
-      <c r="AI17" s="115"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="115"/>
-      <c r="AL17" s="114"/>
-      <c r="AM17" s="115"/>
-      <c r="AN17" s="115"/>
-      <c r="AO17" s="116"/>
-      <c r="AP17" s="119"/>
+      <c r="L26" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="73"/>
+      <c r="U26" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="V26" s="31"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="77"/>
+      <c r="Y26" s="78"/>
+      <c r="Z26" s="78"/>
+      <c r="AA26" s="78"/>
+      <c r="AB26" s="79"/>
+      <c r="AC26" s="23"/>
     </row>
-    <row r="18" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="91"/>
-      <c r="B18" s="120"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="97"/>
-      <c r="S18" s="97"/>
-      <c r="T18" s="97"/>
-      <c r="U18" s="97"/>
-      <c r="V18" s="97"/>
-      <c r="W18" s="97"/>
-      <c r="X18" s="97"/>
-      <c r="Y18" s="97"/>
-      <c r="Z18" s="97"/>
-      <c r="AA18" s="101"/>
-      <c r="AB18" s="102"/>
-      <c r="AF18" s="113"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="114"/>
-      <c r="AI18" s="115"/>
-      <c r="AJ18" s="119"/>
-      <c r="AK18" s="115"/>
-      <c r="AL18" s="115"/>
-      <c r="AM18" s="115"/>
-      <c r="AN18" s="115"/>
-      <c r="AO18" s="116"/>
-      <c r="AP18" s="119"/>
+    <row r="27" spans="1:42" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="54"/>
+      <c r="R27" s="54"/>
+      <c r="S27" s="54"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="74"/>
+      <c r="V27" s="75"/>
+      <c r="W27" s="76"/>
+      <c r="X27" s="80"/>
+      <c r="Y27" s="81"/>
+      <c r="Z27" s="81"/>
+      <c r="AA27" s="81"/>
+      <c r="AB27" s="82"/>
+      <c r="AC27" s="23"/>
     </row>
-    <row r="19" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="103"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="105"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="109"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="107"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="107"/>
-      <c r="T19" s="107"/>
-      <c r="U19" s="107"/>
-      <c r="V19" s="107"/>
-      <c r="W19" s="107"/>
-      <c r="X19" s="107"/>
-      <c r="Y19" s="107"/>
-      <c r="Z19" s="107"/>
-      <c r="AA19" s="111"/>
-      <c r="AB19" s="112"/>
+    <row r="28" spans="1:42" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+      <c r="S28" s="60"/>
+      <c r="T28" s="61"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="34"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="83"/>
+      <c r="Y28" s="84"/>
+      <c r="Z28" s="84"/>
+      <c r="AA28" s="84"/>
+      <c r="AB28" s="85"/>
+      <c r="AC28" s="23"/>
     </row>
-    <row r="20" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="91"/>
-      <c r="B20" s="122"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="97"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="97"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="97"/>
-      <c r="P20" s="100"/>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="97"/>
-      <c r="S20" s="97"/>
-      <c r="T20" s="97"/>
-      <c r="U20" s="97"/>
-      <c r="V20" s="97"/>
-      <c r="W20" s="97"/>
-      <c r="X20" s="97"/>
-      <c r="Y20" s="97"/>
-      <c r="Z20" s="97"/>
-      <c r="AA20" s="101"/>
-      <c r="AB20" s="102"/>
-    </row>
-    <row r="21" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="103"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="107"/>
-      <c r="N21" s="107"/>
-      <c r="O21" s="107"/>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="107"/>
-      <c r="S21" s="107"/>
-      <c r="T21" s="107"/>
-      <c r="U21" s="107"/>
-      <c r="V21" s="107"/>
-      <c r="W21" s="107"/>
-      <c r="X21" s="107"/>
-      <c r="Y21" s="107"/>
-      <c r="Z21" s="107"/>
-      <c r="AA21" s="111"/>
-      <c r="AB21" s="112"/>
-    </row>
-    <row r="22" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="91"/>
-      <c r="B22" s="122"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="97"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="100"/>
-      <c r="Q22" s="97"/>
-      <c r="R22" s="97"/>
-      <c r="S22" s="97"/>
-      <c r="T22" s="97"/>
-      <c r="U22" s="97"/>
-      <c r="V22" s="97"/>
-      <c r="W22" s="97"/>
-      <c r="X22" s="97"/>
-      <c r="Y22" s="97"/>
-      <c r="Z22" s="97"/>
-      <c r="AA22" s="101"/>
-      <c r="AB22" s="102"/>
-    </row>
-    <row r="23" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="103"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="105"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="109"/>
-      <c r="M23" s="107"/>
-      <c r="N23" s="107"/>
-      <c r="O23" s="107"/>
-      <c r="P23" s="110"/>
-      <c r="Q23" s="107"/>
-      <c r="R23" s="107"/>
-      <c r="S23" s="107"/>
-      <c r="T23" s="107"/>
-      <c r="U23" s="107"/>
-      <c r="V23" s="107"/>
-      <c r="W23" s="107"/>
-      <c r="X23" s="107"/>
-      <c r="Y23" s="107"/>
-      <c r="Z23" s="107"/>
-      <c r="AA23" s="111"/>
-      <c r="AB23" s="112"/>
-    </row>
-    <row r="24" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="91"/>
-      <c r="B24" s="122"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="97"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="97"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="97"/>
-      <c r="P24" s="100"/>
-      <c r="Q24" s="97"/>
-      <c r="R24" s="97"/>
-      <c r="S24" s="97"/>
-      <c r="T24" s="97"/>
-      <c r="U24" s="97"/>
-      <c r="V24" s="97"/>
-      <c r="W24" s="97"/>
-      <c r="X24" s="97"/>
-      <c r="Y24" s="97"/>
-      <c r="Z24" s="97"/>
-      <c r="AA24" s="101"/>
-      <c r="AB24" s="102"/>
-    </row>
-    <row r="25" spans="1:42" s="8" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="103"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="107"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="109"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="107"/>
-      <c r="O25" s="107"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="107"/>
-      <c r="R25" s="107"/>
-      <c r="S25" s="107"/>
-      <c r="T25" s="107"/>
-      <c r="U25" s="107"/>
-      <c r="V25" s="107"/>
-      <c r="W25" s="107"/>
-      <c r="X25" s="107"/>
-      <c r="Y25" s="107"/>
-      <c r="Z25" s="107"/>
-      <c r="AA25" s="111"/>
-      <c r="AB25" s="112"/>
-    </row>
-    <row r="26" spans="1:42" s="115" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="124" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="125"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="125"/>
-      <c r="G26" s="125"/>
-      <c r="H26" s="125"/>
-      <c r="I26" s="125"/>
-      <c r="J26" s="127"/>
-      <c r="K26" s="97" t="s">
-        <v>70</v>
-      </c>
-      <c r="L26" s="128" t="s">
-        <v>71</v>
-      </c>
-      <c r="M26" s="129"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="129"/>
-      <c r="P26" s="129"/>
-      <c r="Q26" s="129"/>
-      <c r="R26" s="129"/>
-      <c r="S26" s="129"/>
-      <c r="T26" s="130"/>
-      <c r="U26" s="101" t="s">
-        <v>72</v>
-      </c>
-      <c r="V26" s="131"/>
-      <c r="W26" s="132"/>
-      <c r="X26" s="133"/>
-      <c r="Y26" s="134"/>
-      <c r="Z26" s="134"/>
-      <c r="AA26" s="134"/>
-      <c r="AB26" s="135"/>
-      <c r="AC26" s="136"/>
-    </row>
-    <row r="27" spans="1:42" s="115" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="137" t="s">
+    <row r="29" spans="1:42" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="138"/>
-      <c r="C27" s="138"/>
-      <c r="D27" s="138"/>
-      <c r="E27" s="138"/>
-      <c r="F27" s="138"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="138"/>
-      <c r="I27" s="138"/>
-      <c r="J27" s="139"/>
-      <c r="K27" s="140"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="142"/>
-      <c r="N27" s="142"/>
-      <c r="O27" s="142"/>
-      <c r="P27" s="142"/>
-      <c r="Q27" s="142"/>
-      <c r="R27" s="142"/>
-      <c r="S27" s="142"/>
-      <c r="T27" s="143"/>
-      <c r="U27" s="144"/>
-      <c r="V27" s="145"/>
-      <c r="W27" s="146"/>
-      <c r="X27" s="147"/>
-      <c r="Y27" s="148"/>
-      <c r="Z27" s="148"/>
-      <c r="AA27" s="148"/>
-      <c r="AB27" s="149"/>
-      <c r="AC27" s="136"/>
-    </row>
-    <row r="28" spans="1:42" s="115" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="150" t="s">
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="151"/>
-      <c r="C28" s="151"/>
-      <c r="D28" s="151"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
-      <c r="H28" s="151"/>
-      <c r="I28" s="151"/>
-      <c r="J28" s="152"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="154"/>
-      <c r="N28" s="154"/>
-      <c r="O28" s="154"/>
-      <c r="P28" s="154"/>
-      <c r="Q28" s="154"/>
-      <c r="R28" s="154"/>
-      <c r="S28" s="154"/>
-      <c r="T28" s="155"/>
-      <c r="U28" s="111"/>
-      <c r="V28" s="156"/>
-      <c r="W28" s="157"/>
-      <c r="X28" s="158"/>
-      <c r="Y28" s="159"/>
-      <c r="Z28" s="159"/>
-      <c r="AA28" s="159"/>
-      <c r="AB28" s="160"/>
-      <c r="AC28" s="136"/>
-    </row>
-    <row r="29" spans="1:42" s="115" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="150" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="151"/>
-      <c r="C29" s="151"/>
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
-      <c r="H29" s="151"/>
-      <c r="I29" s="151"/>
-      <c r="J29" s="152"/>
-      <c r="K29" s="140"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="142"/>
-      <c r="N29" s="142"/>
-      <c r="O29" s="142"/>
-      <c r="P29" s="142"/>
-      <c r="Q29" s="142"/>
-      <c r="R29" s="142"/>
-      <c r="S29" s="142"/>
-      <c r="T29" s="143"/>
-      <c r="U29" s="101" t="s">
-        <v>76</v>
-      </c>
-      <c r="V29" s="131"/>
-      <c r="W29" s="132"/>
-      <c r="X29" s="161">
+      <c r="V29" s="31"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="36">
         <f>L5</f>
         <v>45813</v>
       </c>
-      <c r="Y29" s="162"/>
-      <c r="Z29" s="162"/>
-      <c r="AA29" s="162"/>
-      <c r="AB29" s="163"/>
-      <c r="AC29" s="136"/>
+      <c r="Y29" s="37"/>
+      <c r="Z29" s="37"/>
+      <c r="AA29" s="37"/>
+      <c r="AB29" s="38"/>
+      <c r="AC29" s="23"/>
     </row>
-    <row r="30" spans="1:42" s="115" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="164" t="s">
+    <row r="30" spans="1:42" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="47"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="39"/>
+      <c r="Y30" s="40"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="40"/>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="23"/>
+    </row>
+    <row r="31" spans="1:42" s="20" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27"/>
+      <c r="W31" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="165"/>
-      <c r="C30" s="165"/>
-      <c r="D30" s="165"/>
-      <c r="E30" s="165"/>
-      <c r="F30" s="165"/>
-      <c r="G30" s="165"/>
-      <c r="H30" s="165"/>
-      <c r="I30" s="165"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="167"/>
-      <c r="M30" s="168"/>
-      <c r="N30" s="168"/>
-      <c r="O30" s="168"/>
-      <c r="P30" s="168"/>
-      <c r="Q30" s="168"/>
-      <c r="R30" s="168"/>
-      <c r="S30" s="168"/>
-      <c r="T30" s="169"/>
-      <c r="U30" s="111"/>
-      <c r="V30" s="156"/>
-      <c r="W30" s="157"/>
-      <c r="X30" s="170"/>
-      <c r="Y30" s="171"/>
-      <c r="Z30" s="171"/>
-      <c r="AA30" s="171"/>
-      <c r="AB30" s="172"/>
-      <c r="AC30" s="136"/>
+      <c r="X31" s="48"/>
+      <c r="Y31" s="48"/>
+      <c r="Z31" s="48"/>
+      <c r="AA31" s="48"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="28"/>
     </row>
-    <row r="31" spans="1:42" s="115" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="173"/>
-      <c r="B31" s="174"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="174"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="175" t="s">
-        <v>78</v>
-      </c>
-      <c r="I31" s="174"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="176"/>
-      <c r="M31" s="176"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="176"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="176"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="176"/>
-      <c r="T31" s="176"/>
-      <c r="U31" s="176"/>
-      <c r="V31" s="176"/>
-      <c r="W31" s="177" t="s">
-        <v>79</v>
-      </c>
-      <c r="X31" s="177"/>
-      <c r="Y31" s="177"/>
-      <c r="Z31" s="177"/>
-      <c r="AA31" s="177"/>
-      <c r="AB31" s="178"/>
-      <c r="AC31" s="179"/>
-    </row>
-    <row r="32" spans="1:42" s="115" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="180"/>
-      <c r="B32" s="180"/>
-      <c r="C32" s="180"/>
-      <c r="D32" s="180"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="180"/>
-      <c r="G32" s="180"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="180"/>
-      <c r="J32" s="180"/>
-      <c r="K32" s="180"/>
-      <c r="L32" s="136"/>
-      <c r="M32" s="136"/>
-      <c r="N32" s="136"/>
-      <c r="O32" s="136"/>
-      <c r="P32" s="136"/>
-      <c r="Q32" s="136"/>
-      <c r="R32" s="136"/>
-      <c r="S32" s="136"/>
-      <c r="T32" s="136"/>
-      <c r="U32" s="136"/>
-      <c r="V32" s="136"/>
-      <c r="W32" s="136"/>
-      <c r="X32" s="136"/>
-      <c r="Y32" s="136"/>
-      <c r="Z32" s="136"/>
-      <c r="AA32" s="136"/>
-      <c r="AB32" s="136"/>
-      <c r="AC32" s="136"/>
+    <row r="32" spans="1:42" s="20" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="23"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="23"/>
+      <c r="X32" s="23"/>
+      <c r="Y32" s="23"/>
+      <c r="Z32" s="23"/>
+      <c r="AA32" s="23"/>
+      <c r="AB32" s="23"/>
+      <c r="AC32" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="207">
-    <mergeCell ref="U29:W30"/>
-    <mergeCell ref="X29:AB30"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="L30:T30"/>
-    <mergeCell ref="W31:AB31"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="L27:T27"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="L28:T28"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="L29:T29"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="V2:AB2"/>
+    <mergeCell ref="Q3:AB3"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="Q4:AB4"/>
+    <mergeCell ref="Y5:AB6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:K8"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="Q7:W7"/>
+    <mergeCell ref="X7:X13"/>
+    <mergeCell ref="Y7:Y13"/>
+    <mergeCell ref="Z7:Z13"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E5:F6"/>
+    <mergeCell ref="G5:K6"/>
+    <mergeCell ref="L5:P6"/>
+    <mergeCell ref="Q5:X6"/>
+    <mergeCell ref="AA7:AA13"/>
+    <mergeCell ref="AB7:AB13"/>
+    <mergeCell ref="M8:P8"/>
+    <mergeCell ref="Q8:W8"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="E9:E13"/>
+    <mergeCell ref="F9:F13"/>
+    <mergeCell ref="S9:S13"/>
+    <mergeCell ref="T9:T13"/>
+    <mergeCell ref="U9:U13"/>
+    <mergeCell ref="V9:V13"/>
+    <mergeCell ref="W9:W13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="M9:M13"/>
+    <mergeCell ref="N9:N13"/>
+    <mergeCell ref="O9:O13"/>
+    <mergeCell ref="P9:P13"/>
+    <mergeCell ref="Q9:Q13"/>
+    <mergeCell ref="R9:R13"/>
+    <mergeCell ref="G9:G13"/>
+    <mergeCell ref="H9:H13"/>
+    <mergeCell ref="I9:I13"/>
+    <mergeCell ref="J9:J13"/>
+    <mergeCell ref="K9:K13"/>
+    <mergeCell ref="L9:L13"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AB15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AP17:AP18"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AA16:AB17"/>
+    <mergeCell ref="AG17:AG18"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AA18:AB19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="T18:T19"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="V18:V19"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="W20:W21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="AA20:AB21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="V20:V21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="AA22:AB23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Z22:Z23"/>
     <mergeCell ref="W24:W25"/>
     <mergeCell ref="X24:X25"/>
     <mergeCell ref="Y24:Y25"/>
@@ -3879,178 +3974,17 @@
     <mergeCell ref="P24:P25"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="V22:V23"/>
-    <mergeCell ref="W22:W23"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="AA22:AB23"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="T22:T23"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="O22:O23"/>
-    <mergeCell ref="W20:W21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="Y20:Y21"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="AA20:AB21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="V20:V21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="O20:O21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="T18:T19"/>
-    <mergeCell ref="U18:U19"/>
-    <mergeCell ref="V18:V19"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="AJ17:AJ18"/>
-    <mergeCell ref="AP17:AP18"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="AA16:AB17"/>
-    <mergeCell ref="AG17:AG18"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AB19"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="U16:U17"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="AA14:AB15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="S9:S13"/>
-    <mergeCell ref="T9:T13"/>
-    <mergeCell ref="U9:U13"/>
-    <mergeCell ref="V9:V13"/>
-    <mergeCell ref="W9:W13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="M9:M13"/>
-    <mergeCell ref="N9:N13"/>
-    <mergeCell ref="O9:O13"/>
-    <mergeCell ref="P9:P13"/>
-    <mergeCell ref="Q9:Q13"/>
-    <mergeCell ref="R9:R13"/>
-    <mergeCell ref="G9:G13"/>
-    <mergeCell ref="H9:H13"/>
-    <mergeCell ref="I9:I13"/>
-    <mergeCell ref="J9:J13"/>
-    <mergeCell ref="K9:K13"/>
-    <mergeCell ref="L9:L13"/>
-    <mergeCell ref="AA7:AA13"/>
-    <mergeCell ref="AB7:AB13"/>
-    <mergeCell ref="M8:P8"/>
-    <mergeCell ref="Q8:W8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="C9:C13"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="E9:E13"/>
-    <mergeCell ref="F9:F13"/>
-    <mergeCell ref="Y5:AB6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:K8"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="Q7:W7"/>
-    <mergeCell ref="X7:X13"/>
-    <mergeCell ref="Y7:Y13"/>
-    <mergeCell ref="Z7:Z13"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E5:F6"/>
-    <mergeCell ref="G5:K6"/>
-    <mergeCell ref="L5:P6"/>
-    <mergeCell ref="Q5:X6"/>
-    <mergeCell ref="A1:P2"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="V2:AB2"/>
-    <mergeCell ref="Q3:AB3"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="Q4:AB4"/>
+    <mergeCell ref="U29:W30"/>
+    <mergeCell ref="X29:AB30"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="L30:T30"/>
+    <mergeCell ref="W31:AB31"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="L27:T27"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="L28:T28"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="L29:T29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/Na-aba/home/data/가스공사 의뢰서.xlsx
+++ b/Na-aba/home/data/가스공사 의뢰서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjch2\Desktop\보고서\Project PROVIDENCE\Request\PMI\Na-aba\home\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F855A0CD-F07E-4BDE-BC07-E07493CD9A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E87BA1-73E7-48CE-899A-DDEC3FD7F877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3305,7 +3305,7 @@
     <mergeCell ref="L27:T27"/>
     <mergeCell ref="V16:V17"/>
     <mergeCell ref="C5:D6"/>
-    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="W14:W15"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="AP17:AP18"/>
     <mergeCell ref="K9:K13"/>
@@ -3338,7 +3338,7 @@
     <mergeCell ref="K14:K15"/>
     <mergeCell ref="O9:O13"/>
     <mergeCell ref="U14:U15"/>
-    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="R18:R19"/>
     <mergeCell ref="AA16:AB17"/>
     <mergeCell ref="O24:O25"/>
     <mergeCell ref="Y7:Y13"/>
